--- a/Uploads/Data/Rcrt_TEMPLATE.xlsx
+++ b/Uploads/Data/Rcrt_TEMPLATE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erica.Williams\Documents\GitHub\SQL-Database-Corrections\Uploads\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Erica.Levine\Documents\GitHub\SQL-Database-Corrections\Uploads\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1671CCB-B93C-492C-8C3C-46B267F5089B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321668B9-A0A6-4C5C-B1D1-A38E8A7829DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{2108D022-863A-4DDA-9361-349A7F55884E}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{2108D022-863A-4DDA-9361-349A7F55884E}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="2" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5033" uniqueCount="620">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5057" uniqueCount="624">
   <si>
     <t>DataStatus</t>
   </si>
@@ -1920,6 +1920,18 @@
   </si>
   <si>
     <t>ShellID</t>
+  </si>
+  <si>
+    <t>TB Braden South</t>
+  </si>
+  <si>
+    <t>Sex ratio project station</t>
+  </si>
+  <si>
+    <t>Added via SMSS for sex ratio project samples</t>
+  </si>
+  <si>
+    <t>TB Braden South 9</t>
   </si>
 </sst>
 </file>
@@ -2037,36 +2049,21 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="66">
-    <dxf>
-      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="1" formatCode="0"/>
-    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2188,6 +2185,21 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
@@ -2320,40 +2332,40 @@
     <tableColumn id="1" xr3:uid="{76D7ABEC-2288-4626-9B6A-9D01F60F39E0}" name="SampleEventID" dataDxfId="46">
       <calculatedColumnFormula array="1">_xlfn.CONCAT(Instructions!C9,Instructions!A9,"_",TEXT(Instructions!B9,"YYYYMMDD"),"_1_",INDEX(Table1[], MATCH(1,(Table1[Estuary]=Instructions!C9)*(Table1[SectionName]=Instructions!D9)*(Table1[StationNumber]=Instructions!E9)*(Instructions!B9&gt;Table1[StartDate])*(Instructions!B9&lt;Table1[EndDate]),0),1),"_1")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="2" xr3:uid="{9F338ED6-22F6-4E24-AA7D-AC0F8BB69B23}" name="DeployedDate" dataDxfId="0">
+    <tableColumn id="2" xr3:uid="{9F338ED6-22F6-4E24-AA7D-AC0F8BB69B23}" name="DeployedDate" dataDxfId="45">
       <calculatedColumnFormula>Instructions!F9</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{BD967F3C-0D0C-4E5D-80F9-BD1C7E33A66B}" name="ShellReplicate" dataDxfId="4">
+    <tableColumn id="3" xr3:uid="{BD967F3C-0D0C-4E5D-80F9-BD1C7E33A66B}" name="ShellReplicate" dataDxfId="44">
       <calculatedColumnFormula>Instructions!G9</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{36D1E33A-4DE5-4053-922B-6E880D218F24}" name="ShellPosition" dataDxfId="3">
+    <tableColumn id="12" xr3:uid="{36D1E33A-4DE5-4053-922B-6E880D218F24}" name="ShellPosition" dataDxfId="43">
       <calculatedColumnFormula>Instructions!H9</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{D244E709-7C65-411A-9E84-01FD8131200F}" name="NumTop" dataDxfId="2">
+    <tableColumn id="13" xr3:uid="{D244E709-7C65-411A-9E84-01FD8131200F}" name="NumTop" dataDxfId="42">
       <calculatedColumnFormula>Instructions!I9</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{FE22530B-3F54-4A5A-AA63-853CAB9B59A8}" name="NumBottom" dataDxfId="1">
+    <tableColumn id="14" xr3:uid="{FE22530B-3F54-4A5A-AA63-853CAB9B59A8}" name="NumBottom" dataDxfId="41">
       <calculatedColumnFormula>Instructions!J9</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{095E345F-31E0-45E1-A75E-D26E3ADFCB1B}" name="DataStatus" dataDxfId="45">
+    <tableColumn id="17" xr3:uid="{095E345F-31E0-45E1-A75E-D26E3ADFCB1B}" name="DataStatus" dataDxfId="40">
       <calculatedColumnFormula>IF(ISBLANK(Instructions!K9),"",Instructions!K9)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{58F892B1-7D00-4DB4-9264-0B45FFAD448B}" name="DateEntered" dataDxfId="44">
+    <tableColumn id="18" xr3:uid="{58F892B1-7D00-4DB4-9264-0B45FFAD448B}" name="DateEntered" dataDxfId="39">
       <calculatedColumnFormula>IF(ISBLANK(Instructions!L9),"",Instructions!L9)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{49D400BA-2D8E-449C-B429-4D906D77097B}" name="EnteredBy" dataDxfId="43">
+    <tableColumn id="19" xr3:uid="{49D400BA-2D8E-449C-B429-4D906D77097B}" name="EnteredBy" dataDxfId="38">
       <calculatedColumnFormula>IF(ISBLANK(Instructions!M9),"",Instructions!M9)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{AFE53A7E-ADFD-45B7-91C8-ABF7AAF118ED}" name="DateProofed" dataDxfId="42">
+    <tableColumn id="6" xr3:uid="{AFE53A7E-ADFD-45B7-91C8-ABF7AAF118ED}" name="DateProofed" dataDxfId="37">
       <calculatedColumnFormula>IF(ISBLANK(Instructions!N9),"",Instructions!N9)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{9D257618-1409-43E5-B511-606E0EAFAA43}" name="ProofedBy" dataDxfId="41">
+    <tableColumn id="5" xr3:uid="{9D257618-1409-43E5-B511-606E0EAFAA43}" name="ProofedBy" dataDxfId="36">
       <calculatedColumnFormula>IF(ISBLANK(Instructions!O9),"",Instructions!O9)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{31CAB6D2-8900-4335-A113-FA44B7FC3BC8}" name="Comments" dataDxfId="40">
+    <tableColumn id="20" xr3:uid="{31CAB6D2-8900-4335-A113-FA44B7FC3BC8}" name="Comments" dataDxfId="35">
       <calculatedColumnFormula>IF(ISBLANK(Instructions!P9),"",Instructions!P9)</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{B5ED7F1C-175A-40BD-A0D9-4AE0C22437C1}" name="AdminNotes" dataDxfId="39">
+    <tableColumn id="4" xr3:uid="{B5ED7F1C-175A-40BD-A0D9-4AE0C22437C1}" name="AdminNotes" dataDxfId="34">
       <calculatedColumnFormula>Instructions!Q9</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2362,44 +2374,44 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{493C3DDF-B5B4-4E3C-8AD3-ADABB450E83E}" name="Table1" displayName="Table1" ref="A1:AF175" totalsRowShown="0" headerRowDxfId="38" dataDxfId="37">
-  <autoFilter ref="A1:AF175" xr:uid="{493C3DDF-B5B4-4E3C-8AD3-ADABB450E83E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{493C3DDF-B5B4-4E3C-8AD3-ADABB450E83E}" name="Table1" displayName="Table1" ref="A1:AF176" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
+  <autoFilter ref="A1:AF176" xr:uid="{493C3DDF-B5B4-4E3C-8AD3-ADABB450E83E}"/>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:P175">
     <sortCondition ref="A1:A175"/>
   </sortState>
   <tableColumns count="32">
-    <tableColumn id="16" xr3:uid="{61A67C99-3DC3-4EF1-8E9D-4DB22F375E4D}" name="FixedLocationID" dataDxfId="36"/>
-    <tableColumn id="17" xr3:uid="{23398500-7C71-4E68-AC5B-4128DED00607}" name="Estuary" dataDxfId="35"/>
-    <tableColumn id="18" xr3:uid="{22623896-B4D3-46E5-B16B-6F807267A906}" name="SectionName" dataDxfId="34"/>
-    <tableColumn id="1" xr3:uid="{CF8B1BF3-B6B7-4B01-989E-79E6F4B55D09}" name="StationName" dataDxfId="33"/>
-    <tableColumn id="4" xr3:uid="{266FCB90-B3B0-4EB7-8485-44F0794A400C}" name="StationNumber" dataDxfId="32"/>
-    <tableColumn id="5" xr3:uid="{AFB23EC9-14D9-4D70-89C7-BB7CEA80FD07}" name="ParcelName" dataDxfId="31"/>
-    <tableColumn id="6" xr3:uid="{B57A7EB2-6C51-42A1-ACB7-A7205AAB3F91}" name="ParcelArea" dataDxfId="30"/>
-    <tableColumn id="7" xr3:uid="{2C7AFD35-8437-4914-A8E0-A8484E310451}" name="CultchDensity" dataDxfId="29"/>
-    <tableColumn id="8" xr3:uid="{EAFB1F6A-47D9-4B23-827B-C8E89711F378}" name="LatitudeDec" dataDxfId="28"/>
-    <tableColumn id="9" xr3:uid="{8AC47069-6266-4BAC-896C-47A25D67B697}" name="LongitudeDec" dataDxfId="27"/>
-    <tableColumn id="10" xr3:uid="{0C1EBA66-B6C1-4FA5-A28E-C123C64BC674}" name="Recruitment" dataDxfId="26"/>
-    <tableColumn id="11" xr3:uid="{B41AA53E-13E1-49B5-8F9A-50A56B306108}" name="Survey" dataDxfId="25"/>
-    <tableColumn id="12" xr3:uid="{F455ED64-561D-4D37-AACD-F38D2471A77F}" name="Sediment" dataDxfId="24"/>
-    <tableColumn id="13" xr3:uid="{93D4A8C0-0BE8-4884-ADCC-D3A2E6DCF583}" name="Collections" dataDxfId="23"/>
-    <tableColumn id="14" xr3:uid="{3CDA8514-D4DC-4C2A-87C3-5B5727538DA8}" name="ShellBudget" dataDxfId="22"/>
-    <tableColumn id="15" xr3:uid="{D131D469-369A-432F-95FC-15FDC9DED726}" name="Dataloggers" dataDxfId="21"/>
-    <tableColumn id="20" xr3:uid="{F2AE2DD3-34CB-4D7A-B089-C58ABF9918BB}" name="Cage" dataDxfId="20"/>
-    <tableColumn id="21" xr3:uid="{0F2A07B3-E963-449A-9E92-F76C81AAF001}" name="Wave" dataDxfId="19"/>
-    <tableColumn id="22" xr3:uid="{ED629A94-88E6-4E28-A5DA-75F05065A7B9}" name="StartDate" dataDxfId="18"/>
-    <tableColumn id="23" xr3:uid="{48E28D9B-F5A1-48F3-A966-8BEC47D6BFC6}" name="EndDate" dataDxfId="17"/>
-    <tableColumn id="24" xr3:uid="{F0D30C63-87A0-4A31-95B8-CE0FB18EDBB8}" name="DataStatus" dataDxfId="16"/>
-    <tableColumn id="25" xr3:uid="{FDC9CE4F-7A5F-4139-B872-83CBF3DAB490}" name="DateEntered" dataDxfId="15"/>
-    <tableColumn id="26" xr3:uid="{34BC4C5F-8203-4441-B35A-4579EE7DBFD1}" name="EnteredBy" dataDxfId="14"/>
-    <tableColumn id="27" xr3:uid="{414C6AD9-7B8B-477A-A65B-F0BED14C708D}" name="DateProofed" dataDxfId="13"/>
-    <tableColumn id="28" xr3:uid="{B398EA49-5CF4-4D1C-A46D-526A3764E135}" name="ProofedBy" dataDxfId="12"/>
-    <tableColumn id="29" xr3:uid="{214A2D99-CBA5-4226-B426-CCFB3B603394}" name="DateCompleted" dataDxfId="11"/>
-    <tableColumn id="30" xr3:uid="{4AC0CCE6-4D50-46C9-AA6E-A737974E7FA0}" name="CompletedBy" dataDxfId="10"/>
-    <tableColumn id="31" xr3:uid="{F23DB5E6-D6D8-47E6-AD8C-781C08A98666}" name="Comments" dataDxfId="9"/>
-    <tableColumn id="32" xr3:uid="{78696E7B-45A6-41B1-B353-D0BC9F342E5D}" name="AdminNotes" dataDxfId="8"/>
-    <tableColumn id="33" xr3:uid="{1C34CCB0-6EDE-4B04-9CE8-4BB0B1365ADE}" name="StationNameNumber" dataDxfId="7"/>
-    <tableColumn id="34" xr3:uid="{C00DF76D-21B1-40FF-B568-AABD9E194D89}" name="EstuaryLongName" dataDxfId="6"/>
-    <tableColumn id="35" xr3:uid="{C6186EE9-EC39-43A3-8280-B81EB6E9FB93}" name="DateLastCultched" dataDxfId="5"/>
+    <tableColumn id="16" xr3:uid="{61A67C99-3DC3-4EF1-8E9D-4DB22F375E4D}" name="FixedLocationID" dataDxfId="31"/>
+    <tableColumn id="17" xr3:uid="{23398500-7C71-4E68-AC5B-4128DED00607}" name="Estuary" dataDxfId="30"/>
+    <tableColumn id="18" xr3:uid="{22623896-B4D3-46E5-B16B-6F807267A906}" name="SectionName" dataDxfId="29"/>
+    <tableColumn id="1" xr3:uid="{CF8B1BF3-B6B7-4B01-989E-79E6F4B55D09}" name="StationName" dataDxfId="28"/>
+    <tableColumn id="4" xr3:uid="{266FCB90-B3B0-4EB7-8485-44F0794A400C}" name="StationNumber" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{AFB23EC9-14D9-4D70-89C7-BB7CEA80FD07}" name="ParcelName" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{B57A7EB2-6C51-42A1-ACB7-A7205AAB3F91}" name="ParcelArea" dataDxfId="25"/>
+    <tableColumn id="7" xr3:uid="{2C7AFD35-8437-4914-A8E0-A8484E310451}" name="CultchDensity" dataDxfId="24"/>
+    <tableColumn id="8" xr3:uid="{EAFB1F6A-47D9-4B23-827B-C8E89711F378}" name="LatitudeDec" dataDxfId="23"/>
+    <tableColumn id="9" xr3:uid="{8AC47069-6266-4BAC-896C-47A25D67B697}" name="LongitudeDec" dataDxfId="22"/>
+    <tableColumn id="10" xr3:uid="{0C1EBA66-B6C1-4FA5-A28E-C123C64BC674}" name="Recruitment" dataDxfId="21"/>
+    <tableColumn id="11" xr3:uid="{B41AA53E-13E1-49B5-8F9A-50A56B306108}" name="Survey" dataDxfId="20"/>
+    <tableColumn id="12" xr3:uid="{F455ED64-561D-4D37-AACD-F38D2471A77F}" name="Sediment" dataDxfId="19"/>
+    <tableColumn id="13" xr3:uid="{93D4A8C0-0BE8-4884-ADCC-D3A2E6DCF583}" name="Collections" dataDxfId="18"/>
+    <tableColumn id="14" xr3:uid="{3CDA8514-D4DC-4C2A-87C3-5B5727538DA8}" name="ShellBudget" dataDxfId="17"/>
+    <tableColumn id="15" xr3:uid="{D131D469-369A-432F-95FC-15FDC9DED726}" name="Dataloggers" dataDxfId="16"/>
+    <tableColumn id="20" xr3:uid="{F2AE2DD3-34CB-4D7A-B089-C58ABF9918BB}" name="Cage" dataDxfId="15"/>
+    <tableColumn id="21" xr3:uid="{0F2A07B3-E963-449A-9E92-F76C81AAF001}" name="Wave" dataDxfId="14"/>
+    <tableColumn id="22" xr3:uid="{ED629A94-88E6-4E28-A5DA-75F05065A7B9}" name="StartDate" dataDxfId="13"/>
+    <tableColumn id="23" xr3:uid="{48E28D9B-F5A1-48F3-A966-8BEC47D6BFC6}" name="EndDate" dataDxfId="12"/>
+    <tableColumn id="24" xr3:uid="{F0D30C63-87A0-4A31-95B8-CE0FB18EDBB8}" name="DataStatus" dataDxfId="11"/>
+    <tableColumn id="25" xr3:uid="{FDC9CE4F-7A5F-4139-B872-83CBF3DAB490}" name="DateEntered" dataDxfId="10"/>
+    <tableColumn id="26" xr3:uid="{34BC4C5F-8203-4441-B35A-4579EE7DBFD1}" name="EnteredBy" dataDxfId="9"/>
+    <tableColumn id="27" xr3:uid="{414C6AD9-7B8B-477A-A65B-F0BED14C708D}" name="DateProofed" dataDxfId="8"/>
+    <tableColumn id="28" xr3:uid="{B398EA49-5CF4-4D1C-A46D-526A3764E135}" name="ProofedBy" dataDxfId="7"/>
+    <tableColumn id="29" xr3:uid="{214A2D99-CBA5-4226-B426-CCFB3B603394}" name="DateCompleted" dataDxfId="6"/>
+    <tableColumn id="30" xr3:uid="{4AC0CCE6-4D50-46C9-AA6E-A737974E7FA0}" name="CompletedBy" dataDxfId="5"/>
+    <tableColumn id="31" xr3:uid="{F23DB5E6-D6D8-47E6-AD8C-781C08A98666}" name="Comments" dataDxfId="4"/>
+    <tableColumn id="32" xr3:uid="{78696E7B-45A6-41B1-B353-D0BC9F342E5D}" name="AdminNotes" dataDxfId="3"/>
+    <tableColumn id="33" xr3:uid="{1C34CCB0-6EDE-4B04-9CE8-4BB0B1365ADE}" name="StationNameNumber" dataDxfId="2"/>
+    <tableColumn id="34" xr3:uid="{C00DF76D-21B1-40FF-B568-AABD9E194D89}" name="EstuaryLongName" dataDxfId="1"/>
+    <tableColumn id="35" xr3:uid="{C6186EE9-EC39-43A3-8280-B81EB6E9FB93}" name="DateLastCultched" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2738,74 +2750,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
       <c r="H1" s="6"/>
       <c r="I1" s="6"/>
       <c r="J1" s="6"/>
       <c r="K1" s="6"/>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
+      <c r="B2" s="15"/>
+      <c r="C2" s="15"/>
+      <c r="D2" s="15"/>
+      <c r="E2" s="15"/>
+      <c r="F2" s="15"/>
+      <c r="G2" s="15"/>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="14" t="s">
         <v>367</v>
       </c>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
+      <c r="B3" s="15"/>
+      <c r="C3" s="15"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="15"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="15"/>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="14" t="s">
         <v>369</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
+      <c r="B4" s="15"/>
+      <c r="C4" s="15"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="15"/>
+      <c r="F4" s="15"/>
+      <c r="G4" s="15"/>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="14" t="s">
         <v>365</v>
       </c>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
     </row>
     <row r="6" spans="1:17" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="10" t="s">
         <v>368</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+      <c r="G6" s="11"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
@@ -2879,7 +2891,7 @@
       <c r="F9" s="3">
         <v>46028</v>
       </c>
-      <c r="G9" s="14">
+      <c r="G9" s="8">
         <v>1</v>
       </c>
       <c r="H9">
@@ -3341,7 +3353,7 @@
       <c r="G18">
         <v>1</v>
       </c>
-      <c r="H18" s="14">
+      <c r="H18" s="8">
         <v>10</v>
       </c>
       <c r="I18">
@@ -4205,10 +4217,10 @@
       <c r="F35" s="3">
         <v>46028</v>
       </c>
-      <c r="G35" s="14">
+      <c r="G35" s="8">
         <v>3</v>
       </c>
-      <c r="H35" s="14">
+      <c r="H35" s="8">
         <v>3</v>
       </c>
       <c r="I35">
@@ -4256,10 +4268,10 @@
       <c r="F36" s="3">
         <v>46028</v>
       </c>
-      <c r="G36" s="14">
+      <c r="G36" s="8">
         <v>3</v>
       </c>
-      <c r="H36" s="14">
+      <c r="H36" s="8">
         <v>4</v>
       </c>
       <c r="I36">
@@ -4307,10 +4319,10 @@
       <c r="F37" s="3">
         <v>46028</v>
       </c>
-      <c r="G37" s="14">
+      <c r="G37" s="8">
         <v>3</v>
       </c>
-      <c r="H37" s="14">
+      <c r="H37" s="8">
         <v>5</v>
       </c>
       <c r="I37">
@@ -4358,10 +4370,10 @@
       <c r="F38" s="3">
         <v>46028</v>
       </c>
-      <c r="G38" s="14">
+      <c r="G38" s="8">
         <v>3</v>
       </c>
-      <c r="H38" s="14">
+      <c r="H38" s="8">
         <v>6</v>
       </c>
       <c r="I38">
@@ -4409,10 +4421,10 @@
       <c r="F39" s="3">
         <v>46028</v>
       </c>
-      <c r="G39" s="14">
+      <c r="G39" s="8">
         <v>3</v>
       </c>
-      <c r="H39" s="14">
+      <c r="H39" s="8">
         <v>7</v>
       </c>
       <c r="I39">
@@ -4460,10 +4472,10 @@
       <c r="F40" s="3">
         <v>46028</v>
       </c>
-      <c r="G40" s="14">
+      <c r="G40" s="8">
         <v>3</v>
       </c>
-      <c r="H40" s="14">
+      <c r="H40" s="8">
         <v>8</v>
       </c>
       <c r="I40">
@@ -4511,10 +4523,10 @@
       <c r="F41" s="3">
         <v>46028</v>
       </c>
-      <c r="G41" s="14">
+      <c r="G41" s="8">
         <v>3</v>
       </c>
-      <c r="H41" s="14">
+      <c r="H41" s="8">
         <v>9</v>
       </c>
       <c r="I41">
@@ -4562,10 +4574,10 @@
       <c r="F42" s="3">
         <v>46028</v>
       </c>
-      <c r="G42" s="14">
+      <c r="G42" s="8">
         <v>3</v>
       </c>
-      <c r="H42" s="14">
+      <c r="H42" s="8">
         <v>10</v>
       </c>
       <c r="I42">
@@ -4613,10 +4625,10 @@
       <c r="F43" s="3">
         <v>46028</v>
       </c>
-      <c r="G43" s="14">
+      <c r="G43" s="8">
         <v>3</v>
       </c>
-      <c r="H43" s="14">
+      <c r="H43" s="8">
         <v>11</v>
       </c>
       <c r="I43">
@@ -4664,10 +4676,10 @@
       <c r="F44" s="3">
         <v>46028</v>
       </c>
-      <c r="G44" s="15">
+      <c r="G44" s="9">
         <v>3</v>
       </c>
-      <c r="H44" s="15">
+      <c r="H44" s="9">
         <v>12</v>
       </c>
       <c r="I44">
@@ -4790,7 +4802,7 @@
         <f>Instructions!F9</f>
         <v>46028</v>
       </c>
-      <c r="D2" s="14">
+      <c r="D2" s="8">
         <f>Instructions!G9</f>
         <v>1</v>
       </c>
@@ -4848,7 +4860,7 @@
         <f>Instructions!F10</f>
         <v>46028</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="8">
         <f>Instructions!G10</f>
         <v>1</v>
       </c>
@@ -4906,7 +4918,7 @@
         <f>Instructions!F11</f>
         <v>46028</v>
       </c>
-      <c r="D4" s="14">
+      <c r="D4" s="8">
         <f>Instructions!G11</f>
         <v>1</v>
       </c>
@@ -4964,7 +4976,7 @@
         <f>Instructions!F12</f>
         <v>46028</v>
       </c>
-      <c r="D5" s="14">
+      <c r="D5" s="8">
         <f>Instructions!G12</f>
         <v>1</v>
       </c>
@@ -5022,7 +5034,7 @@
         <f>Instructions!F13</f>
         <v>46028</v>
       </c>
-      <c r="D6" s="14">
+      <c r="D6" s="8">
         <f>Instructions!G13</f>
         <v>1</v>
       </c>
@@ -5080,7 +5092,7 @@
         <f>Instructions!F14</f>
         <v>46028</v>
       </c>
-      <c r="D7" s="14">
+      <c r="D7" s="8">
         <f>Instructions!G14</f>
         <v>1</v>
       </c>
@@ -5138,7 +5150,7 @@
         <f>Instructions!F15</f>
         <v>46028</v>
       </c>
-      <c r="D8" s="14">
+      <c r="D8" s="8">
         <f>Instructions!G15</f>
         <v>1</v>
       </c>
@@ -5196,7 +5208,7 @@
         <f>Instructions!F16</f>
         <v>46028</v>
       </c>
-      <c r="D9" s="14">
+      <c r="D9" s="8">
         <f>Instructions!G16</f>
         <v>1</v>
       </c>
@@ -5254,7 +5266,7 @@
         <f>Instructions!F17</f>
         <v>46028</v>
       </c>
-      <c r="D10" s="14">
+      <c r="D10" s="8">
         <f>Instructions!G17</f>
         <v>1</v>
       </c>
@@ -5312,7 +5324,7 @@
         <f>Instructions!F18</f>
         <v>46028</v>
       </c>
-      <c r="D11" s="14">
+      <c r="D11" s="8">
         <f>Instructions!G18</f>
         <v>1</v>
       </c>
@@ -5370,7 +5382,7 @@
         <f>Instructions!F19</f>
         <v>46028</v>
       </c>
-      <c r="D12" s="14">
+      <c r="D12" s="8">
         <f>Instructions!G19</f>
         <v>1</v>
       </c>
@@ -5428,7 +5440,7 @@
         <f>Instructions!F20</f>
         <v>46028</v>
       </c>
-      <c r="D13" s="14">
+      <c r="D13" s="8">
         <f>Instructions!G20</f>
         <v>1</v>
       </c>
@@ -5486,7 +5498,7 @@
         <f>Instructions!F21</f>
         <v>46028</v>
       </c>
-      <c r="D14" s="14">
+      <c r="D14" s="8">
         <f>Instructions!G21</f>
         <v>2</v>
       </c>
@@ -5544,7 +5556,7 @@
         <f>Instructions!F22</f>
         <v>46028</v>
       </c>
-      <c r="D15" s="14">
+      <c r="D15" s="8">
         <f>Instructions!G22</f>
         <v>2</v>
       </c>
@@ -5602,7 +5614,7 @@
         <f>Instructions!F23</f>
         <v>46028</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="8">
         <f>Instructions!G23</f>
         <v>2</v>
       </c>
@@ -5660,7 +5672,7 @@
         <f>Instructions!F24</f>
         <v>46028</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="8">
         <f>Instructions!G24</f>
         <v>2</v>
       </c>
@@ -5718,7 +5730,7 @@
         <f>Instructions!F25</f>
         <v>46028</v>
       </c>
-      <c r="D18" s="14">
+      <c r="D18" s="8">
         <f>Instructions!G25</f>
         <v>2</v>
       </c>
@@ -5776,7 +5788,7 @@
         <f>Instructions!F26</f>
         <v>46028</v>
       </c>
-      <c r="D19" s="14">
+      <c r="D19" s="8">
         <f>Instructions!G26</f>
         <v>2</v>
       </c>
@@ -5834,7 +5846,7 @@
         <f>Instructions!F27</f>
         <v>46028</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="8">
         <f>Instructions!G27</f>
         <v>2</v>
       </c>
@@ -5892,7 +5904,7 @@
         <f>Instructions!F28</f>
         <v>46028</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="8">
         <f>Instructions!G28</f>
         <v>2</v>
       </c>
@@ -5950,7 +5962,7 @@
         <f>Instructions!F29</f>
         <v>46028</v>
       </c>
-      <c r="D22" s="14">
+      <c r="D22" s="8">
         <f>Instructions!G29</f>
         <v>2</v>
       </c>
@@ -6008,7 +6020,7 @@
         <f>Instructions!F30</f>
         <v>46028</v>
       </c>
-      <c r="D23" s="14">
+      <c r="D23" s="8">
         <f>Instructions!G30</f>
         <v>2</v>
       </c>
@@ -6066,7 +6078,7 @@
         <f>Instructions!F31</f>
         <v>46028</v>
       </c>
-      <c r="D24" s="14">
+      <c r="D24" s="8">
         <f>Instructions!G31</f>
         <v>2</v>
       </c>
@@ -6124,7 +6136,7 @@
         <f>Instructions!F32</f>
         <v>46028</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="8">
         <f>Instructions!G32</f>
         <v>2</v>
       </c>
@@ -6182,7 +6194,7 @@
         <f>Instructions!F33</f>
         <v>46028</v>
       </c>
-      <c r="D26" s="14">
+      <c r="D26" s="8">
         <f>Instructions!G33</f>
         <v>3</v>
       </c>
@@ -6240,7 +6252,7 @@
         <f>Instructions!F34</f>
         <v>46028</v>
       </c>
-      <c r="D27" s="14">
+      <c r="D27" s="8">
         <f>Instructions!G34</f>
         <v>3</v>
       </c>
@@ -6298,7 +6310,7 @@
         <f>Instructions!F35</f>
         <v>46028</v>
       </c>
-      <c r="D28" s="14">
+      <c r="D28" s="8">
         <f>Instructions!G35</f>
         <v>3</v>
       </c>
@@ -6356,7 +6368,7 @@
         <f>Instructions!F36</f>
         <v>46028</v>
       </c>
-      <c r="D29" s="14">
+      <c r="D29" s="8">
         <f>Instructions!G36</f>
         <v>3</v>
       </c>
@@ -6414,7 +6426,7 @@
         <f>Instructions!F37</f>
         <v>46028</v>
       </c>
-      <c r="D30" s="14">
+      <c r="D30" s="8">
         <f>Instructions!G37</f>
         <v>3</v>
       </c>
@@ -6472,7 +6484,7 @@
         <f>Instructions!F38</f>
         <v>46028</v>
       </c>
-      <c r="D31" s="14">
+      <c r="D31" s="8">
         <f>Instructions!G38</f>
         <v>3</v>
       </c>
@@ -6530,7 +6542,7 @@
         <f>Instructions!F39</f>
         <v>46028</v>
       </c>
-      <c r="D32" s="14">
+      <c r="D32" s="8">
         <f>Instructions!G39</f>
         <v>3</v>
       </c>
@@ -6588,7 +6600,7 @@
         <f>Instructions!F40</f>
         <v>46028</v>
       </c>
-      <c r="D33" s="14">
+      <c r="D33" s="8">
         <f>Instructions!G40</f>
         <v>3</v>
       </c>
@@ -6646,7 +6658,7 @@
         <f>Instructions!F41</f>
         <v>46028</v>
       </c>
-      <c r="D34" s="14">
+      <c r="D34" s="8">
         <f>Instructions!G41</f>
         <v>3</v>
       </c>
@@ -6704,7 +6716,7 @@
         <f>Instructions!F42</f>
         <v>46028</v>
       </c>
-      <c r="D35" s="14">
+      <c r="D35" s="8">
         <f>Instructions!G42</f>
         <v>3</v>
       </c>
@@ -6762,7 +6774,7 @@
         <f>Instructions!F43</f>
         <v>46028</v>
       </c>
-      <c r="D36" s="14">
+      <c r="D36" s="8">
         <f>Instructions!G43</f>
         <v>3</v>
       </c>
@@ -6820,7 +6832,7 @@
         <f>Instructions!F44</f>
         <v>46028</v>
       </c>
-      <c r="D37" s="14">
+      <c r="D37" s="8">
         <f>Instructions!G44</f>
         <v>3</v>
       </c>
@@ -6875,7 +6887,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9135BC8C-C095-4174-876F-A976B8C1179A}">
-  <dimension ref="A1:AF175"/>
+  <dimension ref="A1:AF176"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" style="2" bestFit="1" customWidth="1"/>
@@ -24062,6 +24074,104 @@
         <v>9</v>
       </c>
     </row>
+    <row r="176" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A176" s="2">
+        <v>401</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>620</v>
+      </c>
+      <c r="E176" s="2">
+        <v>9</v>
+      </c>
+      <c r="F176" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H176" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="I176" s="2">
+        <v>27.495699999999999</v>
+      </c>
+      <c r="J176" s="2">
+        <v>82.523679999999999</v>
+      </c>
+      <c r="K176" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L176" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="M176" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="N176" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="O176" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="P176" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q176" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="R176" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="S176" s="3">
+        <v>46113</v>
+      </c>
+      <c r="T176" s="3">
+        <v>73050</v>
+      </c>
+      <c r="U176" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="V176" s="7">
+        <v>46141</v>
+      </c>
+      <c r="W176" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="X176" s="7">
+        <v>46141</v>
+      </c>
+      <c r="Y176" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="Z176" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AA176" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="AB176" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="AC176" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="AD176" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="AE176" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="AF176" s="2" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
